--- a/outputs/56378.xlsx
+++ b/outputs/56378.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t xml:space="preserve">CODE PRODUCT</t>
   </si>
@@ -55,16 +55,28 @@
     <t xml:space="preserve">Sonatural Frutos Vermelhos</t>
   </si>
   <si>
+    <t xml:space="preserve">S018084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonatural Manga Banana</t>
+  </si>
+  <si>
     <t xml:space="preserve">S018114</t>
   </si>
   <si>
     <t xml:space="preserve">Sonatural Manga/Laranja</t>
   </si>
   <si>
-    <t xml:space="preserve">S018084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonatural Manga Banana</t>
+    <t xml:space="preserve">S018309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonatural Beterraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S018983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonatural Gengibre Ananás</t>
   </si>
   <si>
     <t xml:space="preserve">S018401</t>
@@ -79,12 +91,6 @@
     <t xml:space="preserve">Sonatural Cenoura</t>
   </si>
   <si>
-    <t xml:space="preserve">S018309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonatural Beterraba</t>
-  </si>
-  <si>
     <t xml:space="preserve">S018310</t>
   </si>
   <si>
@@ -101,12 +107,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sonatural Gengibre Maçã</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S018983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonatural Gengibre Ananás</t>
   </si>
   <si>
     <t xml:space="preserve">S018330</t>
@@ -292,9 +292,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -321,7 +327,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="19" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -337,7 +343,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -361,7 +367,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="19" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,16 +383,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="19" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -402,11 +408,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -425,7 +431,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="19" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,7 +451,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="5" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -719,7 +725,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
@@ -821,32 +827,25 @@
       <c r="I5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="4" t="str">
-        <f aca="false" t="array" ref="L5:L5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),1),"")</f>
-        <v>S018133</v>
-      </c>
-      <c r="M5" s="10" t="str">
-        <f aca="false" t="array" ref="M5:M5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),2),"")</f>
-        <v>Sonatural Romã</v>
+      <c r="L5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="N5" s="6" t="n">
-        <f aca="false" t="array" ref="N5:N5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),3),"")</f>
-        <v>0.06</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <f aca="false" t="array" ref="O5:O5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),4),"")</f>
+        <v>0.06</v>
+      </c>
+      <c r="O5" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="P5" s="11" t="n">
-        <f aca="false" t="array" ref="P5:P5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),5),"")</f>
         <v>6</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <f aca="false" t="array" ref="Q5:Q5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),6),"")</f>
         <v>0.469</v>
       </c>
       <c r="R5" s="13" t="n">
-        <f aca="false" t="array" ref="R5:R5">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),1),7),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -870,41 +869,34 @@
         <v>0.25</v>
       </c>
       <c r="I6" s="19"/>
-      <c r="L6" s="20" t="str">
-        <f aca="false" t="array" ref="L6:L6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),1),"")</f>
-        <v>S018084</v>
-      </c>
-      <c r="M6" s="21" t="str">
-        <f aca="false" t="array" ref="M6:M6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),2),"")</f>
-        <v>Sonatural Manga Banana</v>
-      </c>
-      <c r="N6" s="22" t="n">
-        <f aca="false" t="array" ref="N6:N6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),3),"")</f>
-        <v>0.06</v>
-      </c>
-      <c r="O6" s="23" t="n">
-        <f aca="false" t="array" ref="O6:O6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),4),"")</f>
+      <c r="L6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O6" s="22" t="n">
         <v>1.87</v>
       </c>
       <c r="P6" s="23" t="n">
-        <f aca="false" t="array" ref="P6:P6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),5),"")</f>
         <v>2.5</v>
       </c>
       <c r="Q6" s="24" t="n">
-        <f aca="false" t="array" ref="Q6:Q6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),6),"")</f>
         <v>0.33</v>
       </c>
       <c r="R6" s="25" t="n">
-        <f aca="false" t="array" ref="R6:R6">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),2),7),"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>0.06</v>
@@ -919,49 +911,32 @@
         <v>0.24</v>
       </c>
       <c r="I7" s="19"/>
-      <c r="L7" s="20" t="str">
-        <f aca="false" t="array" ref="L7:L7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),1),"")</f>
-        <v>S018309</v>
-      </c>
-      <c r="M7" s="21" t="str">
-        <f aca="false" t="array" ref="M7:M7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),2),"")</f>
-        <v>Sonatural Beterraba</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <f aca="false" t="array" ref="N7:N7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),3),"")</f>
-        <v>0.06</v>
-      </c>
-      <c r="O7" s="23" t="n">
-        <f aca="false" t="array" ref="O7:O7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),4),"")</f>
-        <v>2.54</v>
-      </c>
-      <c r="P7" s="23" t="n">
-        <f aca="false" t="array" ref="P7:P7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),5),"")</f>
-        <v>3.5</v>
-      </c>
-      <c r="Q7" s="24" t="n">
-        <f aca="false" t="array" ref="Q7:Q7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),6),"")</f>
-        <v>0.46</v>
-      </c>
-      <c r="R7" s="25" t="n">
-        <f aca="false" t="array" ref="R7:R7">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),3),7),"")</f>
-        <v>3</v>
-      </c>
+      <c r="L7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="21"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F8" s="27" t="n">
+      <c r="C8" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F8" s="22" t="n">
         <v>1.87</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="H8" s="28" t="n">
@@ -970,41 +945,24 @@
       <c r="I8" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="20" t="str">
-        <f aca="false" t="array" ref="L8:L8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),1),"")</f>
-        <v>S018983</v>
-      </c>
-      <c r="M8" s="21" t="str">
-        <f aca="false" t="array" ref="M8:M8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),2),"")</f>
-        <v>Sonatural Gengibre Ananás</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <f aca="false" t="array" ref="N8:N8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),3),"")</f>
-        <v>0.06</v>
-      </c>
-      <c r="O8" s="23" t="n">
-        <f aca="false" t="array" ref="O8:O8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),4),"")</f>
-        <v>2.65</v>
-      </c>
-      <c r="P8" s="23" t="n">
-        <f aca="false" t="array" ref="P8:P8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),5),"")</f>
-        <v>4</v>
-      </c>
-      <c r="Q8" s="24" t="n">
-        <f aca="false" t="array" ref="Q8:Q8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),6),"")</f>
-        <v>0.15</v>
-      </c>
-      <c r="R8" s="25" t="n">
-        <f aca="false" t="array" ref="R8:R8">IFERROR(INDEX($C$5:$I$21,SMALL(IF($I$5:$I$21&lt;&gt;"",ROW($I$5:$I$21)-ROW($I$5)+1),4),7),"")</f>
-        <v>10</v>
-      </c>
+      <c r="L8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="21"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C9" s="14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0.06</v>
@@ -1029,10 +987,10 @@
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>0.06</v>
@@ -1056,19 +1014,19 @@
       <c r="R10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F11" s="27" t="n">
+      <c r="C11" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F11" s="22" t="n">
         <v>2.54</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="22" t="n">
         <v>3.5</v>
       </c>
       <c r="H11" s="28" t="n">
@@ -1087,10 +1045,10 @@
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>0.06</v>
@@ -1115,10 +1073,10 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0.06</v>
@@ -1143,10 +1101,10 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>0.06</v>
@@ -1170,19 +1128,19 @@
       <c r="R14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F15" s="27" t="n">
+      <c r="C15" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F15" s="22" t="n">
         <v>2.65</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="22" t="n">
         <v>4</v>
       </c>
       <c r="H15" s="28" t="n">
@@ -1260,7 +1218,7 @@
         <v>31</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="16" t="n">
         <v>0.06</v>
@@ -1288,7 +1246,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>0.06</v>
@@ -1316,7 +1274,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E20" s="16" t="n">
         <v>0.06</v>
@@ -1344,7 +1302,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>0.06</v>
@@ -1378,17 +1336,17 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H23" s="36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H24" s="36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="36" t="s">
         <v>35</v>
       </c>
